--- a/apps/festival-pos/template/文化祭レジ_ベビーカステラ_テンプレート.xlsx
+++ b/apps/festival-pos/template/文化祭レジ_ベビーカステラ_テンプレート.xlsx
@@ -1103,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1133,6 +1133,13 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>※「セット以外は常にバラ単価」で計算します。3個・7個ちょうどのときだけセット価格、それ以外は 個数 × バラ単価 です。セットとバラは組み合わせられます。</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -1335,18 +1342,10 @@
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="19" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>※ 商品名がキーです。同じ名前を2行書くと、下の行は無視されます（「レジ管理 → 設定をチェック」が警告します）。※「セット以外は常にバラ単価」で計算します。3個・7個ちょうどのときだけセット価格、それ以外は 個数 × バラ単価 です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A26:F27"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
